--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260728.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260728.xlsx
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>600,000</t>
+          <t>336,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>336,000</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
